--- a/artfynd/A 23464-2023 artfynd.xlsx
+++ b/artfynd/A 23464-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23464-2023 artfynd.xlsx
+++ b/artfynd/A 23464-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80492141</v>
+        <v>80492151</v>
       </c>
       <c r="B2" t="n">
-        <v>83136</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3518</v>
+        <v>1958</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535056.8588643871</v>
+        <v>535029</v>
       </c>
       <c r="R2" t="n">
-        <v>6693447.245937257</v>
+        <v>6693403</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80492146</v>
+        <v>80492141</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>3518</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535053.0057793431</v>
+        <v>535057</v>
       </c>
       <c r="R3" t="n">
-        <v>6693435.833413831</v>
+        <v>6693447</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,19 +840,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,19 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80492134</v>
+        <v>80492130</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535112.2438631606</v>
+        <v>535217</v>
       </c>
       <c r="R4" t="n">
-        <v>6693406.235624045</v>
+        <v>6693410</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,19 +937,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,19 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80492154</v>
+        <v>80492131</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535044.9758502947</v>
+        <v>535142</v>
       </c>
       <c r="R5" t="n">
-        <v>6693395.20006004</v>
+        <v>6693390</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,19 +1034,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80492131</v>
+        <v>80492133</v>
       </c>
       <c r="B6" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535142.1229027855</v>
+        <v>535101</v>
       </c>
       <c r="R6" t="n">
-        <v>6693390.203036946</v>
+        <v>6693397</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1196,19 +1131,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,19 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80492130</v>
+        <v>80492134</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535217.2301561808</v>
+        <v>535112</v>
       </c>
       <c r="R7" t="n">
-        <v>6693410.218921843</v>
+        <v>6693406</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1308,19 +1228,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,19 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>80492140</v>
+        <v>80492138</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535067.2277798039</v>
+        <v>535079</v>
       </c>
       <c r="R8" t="n">
-        <v>6693450.808028011</v>
+        <v>6693437</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1420,19 +1325,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80492155</v>
+        <v>80492140</v>
       </c>
       <c r="B9" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535039.9269375287</v>
+        <v>535067</v>
       </c>
       <c r="R9" t="n">
-        <v>6693405.043108166</v>
+        <v>6693451</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1532,19 +1422,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,16 +1454,11 @@
         <v>80492142</v>
       </c>
       <c r="B10" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535069.2187153219</v>
+        <v>535069</v>
       </c>
       <c r="R10" t="n">
-        <v>6693449.838079146</v>
+        <v>6693450</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1644,19 +1519,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,16 +1551,11 @@
         <v>80492143</v>
       </c>
       <c r="B11" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535054.0441773743</v>
+        <v>535054</v>
       </c>
       <c r="R11" t="n">
-        <v>6693430.897609635</v>
+        <v>6693431</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,19 +1616,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,16 +1648,11 @@
         <v>80492145</v>
       </c>
       <c r="B12" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535045.0277252109</v>
+        <v>535045</v>
       </c>
       <c r="R12" t="n">
-        <v>6693441.196869714</v>
+        <v>6693441</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1868,19 +1713,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>80492135</v>
+        <v>80492146</v>
       </c>
       <c r="B13" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535110.1573432364</v>
+        <v>535053</v>
       </c>
       <c r="R13" t="n">
-        <v>6693417.09633818</v>
+        <v>6693436</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1980,19 +1810,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,16 +1842,11 @@
         <v>80492147</v>
       </c>
       <c r="B14" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2059,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535050.1195263708</v>
+        <v>535050</v>
       </c>
       <c r="R14" t="n">
-        <v>6693426.903098112</v>
+        <v>6693427</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2092,19 +1907,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>80492151</v>
+        <v>80492149</v>
       </c>
       <c r="B15" t="n">
-        <v>90130</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535029.0482113854</v>
+        <v>535027</v>
       </c>
       <c r="R15" t="n">
-        <v>6693402.959898774</v>
+        <v>6693418</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2204,19 +2004,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,19 +2033,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>80492133</v>
+        <v>80492152</v>
       </c>
       <c r="B16" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2283,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535100.9366913995</v>
+        <v>535034</v>
       </c>
       <c r="R16" t="n">
-        <v>6693397.223848783</v>
+        <v>6693410</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2316,19 +2101,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,19 +2130,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>80492152</v>
+        <v>80492154</v>
       </c>
       <c r="B17" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2395,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535033.9350168449</v>
+        <v>535045</v>
       </c>
       <c r="R17" t="n">
-        <v>6693409.931198708</v>
+        <v>6693395</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2428,19 +2198,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,37 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>80492149</v>
+        <v>80492155</v>
       </c>
       <c r="B18" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535026.9238099671</v>
+        <v>535040</v>
       </c>
       <c r="R18" t="n">
-        <v>6693417.776973753</v>
+        <v>6693405</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2540,19 +2295,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>80492138</v>
+        <v>75945939</v>
       </c>
       <c r="B19" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90681</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,37 +2335,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6268</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Kumm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Dammsjöns naturreservat, Dlr</t>
+          <t>Dammsjöns NR, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535078.7544310269</v>
+        <v>535172</v>
       </c>
       <c r="R19" t="n">
-        <v>6693437.071007486</v>
+        <v>6693320</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2649,22 +2398,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-08-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-08-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>1 ex. under gran, intill en stig.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2675,19 +2419,699 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Talldominerad sandbarrskog.</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>80083208</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Dammsjön NR, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>535249</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6693281</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gustafs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2019-09-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2019-09-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>äldre tallbestånd</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>80083214</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Dammsjön NR, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>535227</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6693289</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gustafs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2019-09-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2019-09-24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>äldre tallbestånd</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>96144669</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Dammsjön NR, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>535294</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6693412</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gustafs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>lingonristyp</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>ogallrad tallungskog # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>112020521</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Dammsjön NR, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>535178</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6693464</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gustafs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-09-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-09-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Avverkningsanmält</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128550136</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Dammsjön NR, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>535321</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6693288</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gustafs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>ristyp</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23464-2023 artfynd.xlsx
+++ b/artfynd/A 23464-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80492151</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80492141</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80492130</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80492131</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80492133</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80492134</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80492138</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80492140</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80492142</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80492143</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80492145</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80492146</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80492147</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80492149</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80492152</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80492154</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80492155</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2437,6 +2527,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75945939</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2571,6 +2666,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80083208</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2705,6 +2805,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80083214</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2839,6 +2944,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96144669</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2978,6 +3088,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112020521</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3112,8 +3227,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128550136</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>